--- a/output/laminas_comunales/comunal_i_ingr_median_a_2022_aysen.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2022_aysen.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>849057.5</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>807992</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>792811</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>786430</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>772243.5</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>750000</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>687870</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>680355</v>
       </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>679625</v>
       </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -512,9 +480,6 @@
       </c>
       <c r="B11">
         <v>622720</v>
-      </c>
-      <c r="F11" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2022_aysen.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2022_aysen.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>849057.5</v>
       </c>
+      <c r="C2">
+        <v>789697</v>
+      </c>
+      <c r="D2">
+        <v>59360.5</v>
+      </c>
+      <c r="E2">
+        <v>7.516870394594388</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -401,6 +410,15 @@
       <c r="B3">
         <v>807992</v>
       </c>
+      <c r="C3">
+        <v>691990.5</v>
+      </c>
+      <c r="D3">
+        <v>116001.5</v>
+      </c>
+      <c r="E3">
+        <v>16.76345267745727</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -411,6 +429,15 @@
       <c r="B4">
         <v>792811</v>
       </c>
+      <c r="C4">
+        <v>709152</v>
+      </c>
+      <c r="D4">
+        <v>83659</v>
+      </c>
+      <c r="E4">
+        <v>11.7970477415279</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -421,64 +448,137 @@
       <c r="B5">
         <v>786430</v>
       </c>
+      <c r="C5">
+        <v>723048</v>
+      </c>
+      <c r="D5">
+        <v>63382</v>
+      </c>
+      <c r="E5">
+        <v>8.765946382536161</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Chile Chico</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B6">
-        <v>772243.5</v>
+        <v>783100</v>
+      </c>
+      <c r="C6">
+        <v>703134</v>
+      </c>
+      <c r="D6">
+        <v>79966</v>
+      </c>
+      <c r="E6">
+        <v>11.3727966504251</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cisnes</t>
+          <t>Chile Chico</t>
         </is>
       </c>
       <c r="B7">
-        <v>750000</v>
+        <v>772243.5</v>
+      </c>
+      <c r="C7">
+        <v>681300</v>
+      </c>
+      <c r="D7">
+        <v>90943.5</v>
+      </c>
+      <c r="E7">
+        <v>13.34852487890796</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Guaitecas</t>
+          <t>Cisnes</t>
         </is>
       </c>
       <c r="B8">
-        <v>687870</v>
+        <v>750000</v>
+      </c>
+      <c r="C8">
+        <v>668800.5</v>
+      </c>
+      <c r="D8">
+        <v>81199.5</v>
+      </c>
+      <c r="E8">
+        <v>12.14106448784054</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Río Ibáñez</t>
+          <t>Guaitecas</t>
         </is>
       </c>
       <c r="B9">
-        <v>680355</v>
+        <v>687870</v>
+      </c>
+      <c r="C9">
+        <v>646099</v>
+      </c>
+      <c r="D9">
+        <v>41771</v>
+      </c>
+      <c r="E9">
+        <v>6.46510828835829</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lago Verde</t>
+          <t>Río Ibáñez</t>
         </is>
       </c>
       <c r="B10">
-        <v>679625</v>
+        <v>680355</v>
+      </c>
+      <c r="C10">
+        <v>580000</v>
+      </c>
+      <c r="D10">
+        <v>100355</v>
+      </c>
+      <c r="E10">
+        <v>17.30258620689655</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O Higgins</t>
+          <t>Lago Verde</t>
         </is>
       </c>
       <c r="B11">
+        <v>679625</v>
+      </c>
+      <c r="C11">
+        <v>632779</v>
+      </c>
+      <c r="D11">
+        <v>46846</v>
+      </c>
+      <c r="E11">
+        <v>7.403216604849394</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="B12">
         <v>622720</v>
       </c>
     </row>
@@ -577,7 +677,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="B9">

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2022_aysen.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2022_aysen.xlsx
@@ -589,7 +589,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -598,20 +598,12 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aysén</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>786430</v>
+          <t>Río Ibáñez</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -620,88 +612,61 @@
           <t>Chile Chico</t>
         </is>
       </c>
-      <c r="B3">
-        <v>772243.5</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cisnes</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>750000</v>
+          <t>Lago Verde</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cochrane</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>807992</v>
+          <t>Coyhaique</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coyhaique</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>792811</v>
+          <t>Cisnes</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Guaitecas</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>687870</v>
+          <t>Tortel</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lago Verde</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>679625</v>
+          <t>O'Higgins</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>622720</v>
+          <t>Cochrane</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Río Ibáñez</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>680355</v>
+          <t>Guaitecas</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tortel</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>849057.5</v>
+          <t>Aysén</t>
+        </is>
       </c>
     </row>
   </sheetData>
